--- a/artfynd/A 60586-2025 artfynd.xlsx
+++ b/artfynd/A 60586-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128053276</v>
       </c>
       <c r="B2" t="n">
-        <v>96708</v>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,6 +788,253 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126571271</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Linkonkalli, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>361349</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6657053</v>
+      </c>
+      <c r="S3" t="n">
+        <v>26</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bogen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>208 ex på en sträcka av 100 meter. Ståendes på båda sidor av vägen i ytterslänt, innerslänt och bankslänt.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Malin Schött, Maria Magnusson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129012210</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kyrkskog, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>361344</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6657055</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bogen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Står spritt på en sträcka av 100 meter på båda sidor av vägen i ytterslänt, innerslänt och bankslänt.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Magnusson, Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
